--- a/artfynd/A 5107-2026 artfynd.xlsx
+++ b/artfynd/A 5107-2026 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131118221</v>
+        <v>131449357</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>91837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,42 +903,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Lidmyran, Vb</t>
+          <t>Lidmyrbrännan, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730980</v>
+        <v>731060</v>
       </c>
       <c r="R4" t="n">
-        <v>7122728</v>
+        <v>7122797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,14 +956,19 @@
           <t>2026-02-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,22 +983,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131449357</v>
+        <v>131118221</v>
       </c>
       <c r="B5" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,30 +1006,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lidmyrbrännan, Vb</t>
+          <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>731060</v>
+        <v>730980</v>
       </c>
       <c r="R5" t="n">
-        <v>7122797</v>
+        <v>7122728</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,19 +1071,14 @@
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:28</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,12 +1093,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 5107-2026 artfynd.xlsx
+++ b/artfynd/A 5107-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131118218</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131449355</v>
       </c>
       <c r="B3" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131449357</v>
+        <v>131118221</v>
       </c>
       <c r="B4" t="n">
-        <v>91837</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,30 +903,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lidmyrbrännan, Vb</t>
+          <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>731060</v>
+        <v>730980</v>
       </c>
       <c r="R4" t="n">
-        <v>7122797</v>
+        <v>7122728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,19 +968,14 @@
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:28</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,22 +990,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131118221</v>
+        <v>131449357</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>91838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,42 +1013,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Lidmyran, Vb</t>
+          <t>Lidmyrbrännan, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730980</v>
+        <v>731060</v>
       </c>
       <c r="R5" t="n">
-        <v>7122728</v>
+        <v>7122797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,14 +1066,19 @@
           <t>2026-02-08</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,12 +1093,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1108,7 +1108,7 @@
         <v>131118223</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>131118216</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>131118220</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>131118225</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>131118224</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>131118226</v>
       </c>
       <c r="B11" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>131118212</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>131449360</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>131118217</v>
       </c>
       <c r="B14" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>131118213</v>
       </c>
       <c r="B15" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 5107-2026 artfynd.xlsx
+++ b/artfynd/A 5107-2026 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131118221</v>
+        <v>131449357</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,42 +903,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Lidmyran, Vb</t>
+          <t>Lidmyrbrännan, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730980</v>
+        <v>731060</v>
       </c>
       <c r="R4" t="n">
-        <v>7122728</v>
+        <v>7122797</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,14 +956,19 @@
           <t>2026-02-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,22 +983,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131449357</v>
+        <v>131118221</v>
       </c>
       <c r="B5" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1013,30 +1006,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lidmyrbrännan, Vb</t>
+          <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>731060</v>
+        <v>730980</v>
       </c>
       <c r="R5" t="n">
-        <v>7122797</v>
+        <v>7122728</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,19 +1071,14 @@
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:28</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:28</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,12 +1093,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 5107-2026 artfynd.xlsx
+++ b/artfynd/A 5107-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131118218</v>
+        <v>131449355</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>91814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stor-Lidmyran, Vb</t>
+          <t>Lidmyrbrännan, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730971</v>
+        <v>731032</v>
       </c>
       <c r="R2" t="n">
-        <v>7122743</v>
+        <v>7122755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,14 +743,19 @@
           <t>2026-02-08</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131449355</v>
+        <v>131449357</v>
       </c>
       <c r="B3" t="n">
-        <v>91814</v>
+        <v>91838</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,23 +793,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -820,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>731032</v>
+        <v>731060</v>
       </c>
       <c r="R3" t="n">
-        <v>7122755</v>
+        <v>7122797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,7 +848,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -865,7 +858,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131449357</v>
+        <v>131449360</v>
       </c>
       <c r="B4" t="n">
-        <v>91838</v>
+        <v>79250</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,19 +896,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>731060</v>
+        <v>730932</v>
       </c>
       <c r="R4" t="n">
-        <v>7122797</v>
+        <v>7122956</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,7 +955,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -968,7 +965,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,7 +992,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131118221</v>
+        <v>131118218</v>
       </c>
       <c r="B5" t="n">
         <v>57888</v>
@@ -1038,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730980</v>
+        <v>730971</v>
       </c>
       <c r="R5" t="n">
-        <v>7122728</v>
+        <v>7122743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1102,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131118223</v>
+        <v>131118221</v>
       </c>
       <c r="B6" t="n">
         <v>57888</v>
@@ -1148,10 +1145,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730999</v>
+        <v>730980</v>
       </c>
       <c r="R6" t="n">
-        <v>7122715</v>
+        <v>7122728</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131118216</v>
+        <v>131118223</v>
       </c>
       <c r="B7" t="n">
         <v>57888</v>
@@ -1258,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730959</v>
+        <v>730999</v>
       </c>
       <c r="R7" t="n">
-        <v>7122758</v>
+        <v>7122715</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131118220</v>
+        <v>131118216</v>
       </c>
       <c r="B8" t="n">
         <v>57888</v>
@@ -1368,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730978</v>
+        <v>730959</v>
       </c>
       <c r="R8" t="n">
-        <v>7122735</v>
+        <v>7122758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1432,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131118225</v>
+        <v>131118220</v>
       </c>
       <c r="B9" t="n">
         <v>57888</v>
@@ -1478,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730988</v>
+        <v>730978</v>
       </c>
       <c r="R9" t="n">
-        <v>7122720</v>
+        <v>7122735</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,7 +1542,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131118224</v>
+        <v>131118225</v>
       </c>
       <c r="B10" t="n">
         <v>57888</v>
@@ -1588,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730994</v>
+        <v>730988</v>
       </c>
       <c r="R10" t="n">
-        <v>7122716</v>
+        <v>7122720</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131118226</v>
+        <v>131118224</v>
       </c>
       <c r="B11" t="n">
-        <v>91814</v>
+        <v>57888</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1666,34 +1663,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>731023</v>
+        <v>730994</v>
       </c>
       <c r="R11" t="n">
-        <v>7122947</v>
+        <v>7122716</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,6 +1731,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131118212</v>
+        <v>131118226</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>91814</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,42 +1773,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730937</v>
+        <v>731023</v>
       </c>
       <c r="R12" t="n">
-        <v>7122782</v>
+        <v>7122947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,11 +1833,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131449360</v>
+        <v>131118212</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,34 +1870,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lidmyrbrännan, Vb</t>
+          <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730932</v>
+        <v>730937</v>
       </c>
       <c r="R13" t="n">
-        <v>7122956</v>
+        <v>7122782</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,19 +1935,14 @@
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:59</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1957,12 +1957,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 5107-2026 artfynd.xlsx
+++ b/artfynd/A 5107-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131449355</v>
       </c>
       <c r="B2" t="n">
-        <v>91814</v>
+        <v>91817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131449357</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131449360</v>
       </c>
       <c r="B4" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>131118218</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>131118221</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>131118223</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>131118216</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>131118220</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>131118225</v>
       </c>
       <c r="B10" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>131118224</v>
       </c>
       <c r="B11" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>131118226</v>
       </c>
       <c r="B12" t="n">
-        <v>91814</v>
+        <v>91817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>131118212</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>131118217</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>131118213</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 5107-2026 artfynd.xlsx
+++ b/artfynd/A 5107-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131449355</v>
       </c>
       <c r="B2" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131449357</v>
       </c>
       <c r="B3" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131449360</v>
       </c>
       <c r="B4" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>131118218</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>131118221</v>
       </c>
       <c r="B6" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>131118223</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>131118216</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>131118220</v>
       </c>
       <c r="B9" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>131118225</v>
       </c>
       <c r="B10" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>131118224</v>
       </c>
       <c r="B11" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>131118226</v>
       </c>
       <c r="B12" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>131118212</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>131118217</v>
       </c>
       <c r="B14" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>131118213</v>
       </c>
       <c r="B15" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 5107-2026 artfynd.xlsx
+++ b/artfynd/A 5107-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131449355</v>
       </c>
       <c r="B2" t="n">
-        <v>91818</v>
+        <v>91824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131449357</v>
       </c>
       <c r="B3" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131449360</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>131118218</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>131118221</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>131118223</v>
       </c>
       <c r="B7" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>131118216</v>
       </c>
       <c r="B8" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>131118220</v>
       </c>
       <c r="B9" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>131118225</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>131118224</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131118226</v>
+        <v>131118212</v>
       </c>
       <c r="B12" t="n">
-        <v>91818</v>
+        <v>57898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,34 +1773,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>731023</v>
+        <v>730937</v>
       </c>
       <c r="R12" t="n">
-        <v>7122947</v>
+        <v>7122782</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,6 +1841,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131118212</v>
+        <v>131118226</v>
       </c>
       <c r="B13" t="n">
-        <v>57892</v>
+        <v>91824</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,42 +1883,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730937</v>
+        <v>731023</v>
       </c>
       <c r="R13" t="n">
-        <v>7122782</v>
+        <v>7122947</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,11 +1943,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,7 +1972,7 @@
         <v>131118217</v>
       </c>
       <c r="B14" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>131118213</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 5107-2026 artfynd.xlsx
+++ b/artfynd/A 5107-2026 artfynd.xlsx
@@ -1762,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131118212</v>
+        <v>131118226</v>
       </c>
       <c r="B12" t="n">
-        <v>57898</v>
+        <v>91824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,42 +1773,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730937</v>
+        <v>731023</v>
       </c>
       <c r="R12" t="n">
-        <v>7122782</v>
+        <v>7122947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,11 +1833,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131118226</v>
+        <v>131118212</v>
       </c>
       <c r="B13" t="n">
-        <v>91824</v>
+        <v>57898</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,34 +1870,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>731023</v>
+        <v>730937</v>
       </c>
       <c r="R13" t="n">
-        <v>7122947</v>
+        <v>7122782</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,6 +1938,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 5107-2026 artfynd.xlsx
+++ b/artfynd/A 5107-2026 artfynd.xlsx
@@ -1322,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131118216</v>
+        <v>131118220</v>
       </c>
       <c r="B8" t="n">
         <v>57898</v>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730959</v>
+        <v>730978</v>
       </c>
       <c r="R8" t="n">
-        <v>7122758</v>
+        <v>7122735</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131118220</v>
+        <v>131118216</v>
       </c>
       <c r="B9" t="n">
         <v>57898</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730978</v>
+        <v>730959</v>
       </c>
       <c r="R9" t="n">
-        <v>7122735</v>
+        <v>7122758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 5107-2026 artfynd.xlsx
+++ b/artfynd/A 5107-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131449355</v>
       </c>
       <c r="B2" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131449357</v>
       </c>
       <c r="B3" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131449360</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>131118218</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>131118221</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>131118223</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131118220</v>
+        <v>131118216</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730978</v>
+        <v>730959</v>
       </c>
       <c r="R8" t="n">
-        <v>7122735</v>
+        <v>7122758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131118216</v>
+        <v>131118220</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730959</v>
+        <v>730978</v>
       </c>
       <c r="R9" t="n">
-        <v>7122758</v>
+        <v>7122735</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1545,7 +1545,7 @@
         <v>131118225</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>131118224</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131118226</v>
+        <v>131118212</v>
       </c>
       <c r="B12" t="n">
-        <v>91824</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,34 +1773,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>731023</v>
+        <v>730937</v>
       </c>
       <c r="R12" t="n">
-        <v>7122947</v>
+        <v>7122782</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,6 +1841,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131118212</v>
+        <v>131118226</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>91825</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,42 +1883,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730937</v>
+        <v>731023</v>
       </c>
       <c r="R13" t="n">
-        <v>7122782</v>
+        <v>7122947</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,11 +1943,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,7 +1972,7 @@
         <v>131118217</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>131118213</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 5107-2026 artfynd.xlsx
+++ b/artfynd/A 5107-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131449355</v>
       </c>
       <c r="B2" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131449357</v>
       </c>
       <c r="B3" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131449360</v>
       </c>
       <c r="B4" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>131118218</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>131118221</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>131118223</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>131118216</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>131118220</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>131118225</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>131118224</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131118212</v>
+        <v>131118226</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>91828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1773,42 +1773,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730937</v>
+        <v>731023</v>
       </c>
       <c r="R12" t="n">
-        <v>7122782</v>
+        <v>7122947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,11 +1833,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131118226</v>
+        <v>131118212</v>
       </c>
       <c r="B13" t="n">
-        <v>91825</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,34 +1870,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Lidmyran, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>731023</v>
+        <v>730937</v>
       </c>
       <c r="R13" t="n">
-        <v>7122947</v>
+        <v>7122782</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1943,6 +1938,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,7 +1972,7 @@
         <v>131118217</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>131118213</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 5107-2026 artfynd.xlsx
+++ b/artfynd/A 5107-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131449355</v>
       </c>
       <c r="B2" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131449357</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>131449360</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>131118218</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>131118221</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>131118223</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>131118216</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>131118220</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>131118225</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>131118224</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>131118226</v>
       </c>
       <c r="B12" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>131118212</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>131118217</v>
       </c>
       <c r="B14" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>131118213</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
